--- a/ITTKI_Nazorat/docs/samples/BHMS_MHXS_solishtirma.xlsx
+++ b/ITTKI_Nazorat/docs/samples/BHMS_MHXS_solishtirma.xlsx
@@ -512,7 +512,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Tuzilgan: 11.10.2026 16:41 · ITTKI Nazorat</t>
+          <t>Tuzilgan: 12.10.2026 05:41 · ITTKI Nazorat</t>
         </is>
       </c>
     </row>

--- a/ITTKI_Nazorat/docs/samples/BHMS_MHXS_solishtirma.xlsx
+++ b/ITTKI_Nazorat/docs/samples/BHMS_MHXS_solishtirma.xlsx
@@ -512,7 +512,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Tuzilgan: 12.10.2026 05:41 · ITTKI Nazorat</t>
+          <t>Tuzilgan: 11.10.2026 10:00:30 (Toshkent, UTC+5) · ITTKI Nazorat</t>
         </is>
       </c>
     </row>
